--- a/data/reina/inputs/reina-hellsweep_WRA_plus6.xlsx
+++ b/data/reina/inputs/reina-hellsweep_WRA_plus6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\reina\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B39640-55C2-41A2-98CF-D3D518D079BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50484FB3-94C0-4B6B-BB14-026E5380E281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="1755" windowWidth="19320" windowHeight="11925" activeTab="1" xr2:uid="{2CC25222-CDB9-46F9-96C2-21E530B6B423}"/>
+    <workbookView xWindow="2880" yWindow="2385" windowWidth="24990" windowHeight="11925" activeTab="1" xr2:uid="{2CC25222-CDB9-46F9-96C2-21E530B6B423}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>key</t>
   </si>
@@ -121,13 +121,19 @@
   </si>
   <si>
     <t>WGS.4,2</t>
+  </si>
+  <si>
+    <t>Crouch Jab</t>
+  </si>
+  <si>
+    <t>Power Crush</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,13 +141,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -153,13 +171,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -546,16 +567,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8145A058-A636-45A1-A5EA-BCF72CFAB74E}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -580,8 +603,14 @@
       <c r="H1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -606,8 +635,14 @@
       <c r="H2">
         <v>-80</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>-5</v>
+      </c>
+      <c r="J2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -632,8 +667,14 @@
       <c r="H3">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>36</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -658,8 +699,14 @@
       <c r="H4">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>31</v>
+      </c>
+      <c r="J4">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -684,8 +731,14 @@
       <c r="H5">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>-6</v>
+      </c>
+      <c r="J5">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -710,8 +763,14 @@
       <c r="H6">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>36</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -736,8 +795,14 @@
       <c r="H7">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <v>-6</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -762,8 +827,14 @@
       <c r="H8">
         <v>-76</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8">
+        <v>-6</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -788,8 +859,14 @@
       <c r="H9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -814,10 +891,43 @@
       <c r="H10">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <v>-6</v>
+      </c>
+      <c r="J10">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
+      </c>
+      <c r="B11" s="1">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>-76</v>
+      </c>
+      <c r="D11">
+        <v>-24</v>
+      </c>
+      <c r="E11" s="1">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1">
+        <v>33</v>
+      </c>
+      <c r="G11" s="1">
+        <v>33</v>
+      </c>
+      <c r="H11">
+        <v>-76</v>
+      </c>
+      <c r="I11" s="1">
+        <v>33</v>
+      </c>
+      <c r="J11">
+        <v>-17</v>
       </c>
     </row>
   </sheetData>
